--- a/xlsx/tests/calc_tests/TEXT/MID_LEFT_RIGHT_arrays.xlsx
+++ b/xlsx/tests/calc_tests/TEXT/MID_LEFT_RIGHT_arrays.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nhatcher/IronCalc/IronCalc/xlsx/tests/calc_tests/TEXT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159426F9-DBA3-9B4F-9FAE-95EADCADDD08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7BA0F8-89F1-074E-87F7-3199B9D72652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14240" yWindow="-20980" windowWidth="19220" windowHeight="20980" xr2:uid="{E3987B39-FA4C-9143-9055-F3991595AEA1}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -466,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB4F765-0F42-1042-8B10-1E5BEEFE9E28}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -916,19 +916,40 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G33" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="34" spans="7:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G34" t="e">
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="35" spans="7:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G35" t="e">
         <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" t="e">
+        <f>REPLACE("abc", "NaN", 1, "x")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" t="e" cm="1">
+        <f t="array" ref="A41:B41">REPLACE("abc", {"NaN",2}, 1, "x")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B41" t="str">
+        <v>axc</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" t="e">
+        <f>SUBSTITUTE("a-b-c", "-", "+", "NaN")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
